--- a/artfynd/A 14829-2025 artfynd.xlsx
+++ b/artfynd/A 14829-2025 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125017099</v>
+        <v>125017103</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>92293</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,31 +794,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -827,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465919</v>
+        <v>465884</v>
       </c>
       <c r="R3" t="n">
-        <v>6772218</v>
+        <v>6772194</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -991,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125017103</v>
+        <v>125017099</v>
       </c>
       <c r="B5" t="n">
-        <v>92293</v>
+        <v>57529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,35 +1007,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465884</v>
+        <v>465919</v>
       </c>
       <c r="R5" t="n">
-        <v>6772194</v>
+        <v>6772218</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 14829-2025 artfynd.xlsx
+++ b/artfynd/A 14829-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125017100</v>
+        <v>125017103</v>
       </c>
       <c r="B2" t="n">
-        <v>92328</v>
+        <v>92293</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kvarntjärn, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465685</v>
+        <v>465884</v>
       </c>
       <c r="R2" t="n">
-        <v>6771959</v>
+        <v>6772194</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +760,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-12</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125017103</v>
+        <v>125017099</v>
       </c>
       <c r="B3" t="n">
-        <v>92293</v>
+        <v>57529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,35 +798,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465884</v>
+        <v>465919</v>
       </c>
       <c r="R3" t="n">
-        <v>6772194</v>
+        <v>6772218</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -995,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125017099</v>
+        <v>125017104</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
+        <v>92293</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,31 +1007,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1040,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465919</v>
+        <v>465886</v>
       </c>
       <c r="R5" t="n">
-        <v>6772218</v>
+        <v>6772198</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1102,10 +1106,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125017104</v>
+        <v>125017100</v>
       </c>
       <c r="B6" t="n">
-        <v>92293</v>
+        <v>92328</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,47 +1118,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kvarntjärn, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465886</v>
+        <v>465685</v>
       </c>
       <c r="R6" t="n">
-        <v>6772198</v>
+        <v>6771959</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1187,6 +1182,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 14829-2025 artfynd.xlsx
+++ b/artfynd/A 14829-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125017103</v>
+        <v>125017104</v>
       </c>
       <c r="B2" t="n">
         <v>92293</v>
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465884</v>
+        <v>465886</v>
       </c>
       <c r="R2" t="n">
-        <v>6772194</v>
+        <v>6772198</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125017099</v>
+        <v>125017102</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,39 +802,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kvarntjärn, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465919</v>
+        <v>465660</v>
       </c>
       <c r="R3" t="n">
-        <v>6772218</v>
+        <v>6771995</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125017102</v>
+        <v>125017100</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>92328</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,21 +904,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -933,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465660</v>
+        <v>465685</v>
       </c>
       <c r="R4" t="n">
-        <v>6771995</v>
+        <v>6771959</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,6 +964,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -995,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125017104</v>
+        <v>125017099</v>
       </c>
       <c r="B5" t="n">
-        <v>92293</v>
+        <v>57529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,35 +1007,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1044,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465886</v>
+        <v>465919</v>
       </c>
       <c r="R5" t="n">
-        <v>6772198</v>
+        <v>6772218</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,10 +1102,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125017100</v>
+        <v>125017103</v>
       </c>
       <c r="B6" t="n">
-        <v>92328</v>
+        <v>92293</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1118,38 +1114,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kvarntjärn, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465685</v>
+        <v>465884</v>
       </c>
       <c r="R6" t="n">
-        <v>6771959</v>
+        <v>6772194</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1182,11 +1187,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-12</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 14829-2025 artfynd.xlsx
+++ b/artfynd/A 14829-2025 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125017102</v>
+        <v>125017100</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>92328</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465660</v>
+        <v>465685</v>
       </c>
       <c r="R3" t="n">
-        <v>6771995</v>
+        <v>6771959</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,6 +862,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125017100</v>
+        <v>125017103</v>
       </c>
       <c r="B4" t="n">
-        <v>92328</v>
+        <v>92293</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,38 +905,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kvarntjärn, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465685</v>
+        <v>465884</v>
       </c>
       <c r="R4" t="n">
-        <v>6771959</v>
+        <v>6772194</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,11 +978,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-12</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -995,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125017099</v>
+        <v>125017102</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,39 +1020,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kvarntjärn, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465919</v>
+        <v>465660</v>
       </c>
       <c r="R5" t="n">
-        <v>6772218</v>
+        <v>6771995</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1102,10 +1106,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125017103</v>
+        <v>125017099</v>
       </c>
       <c r="B6" t="n">
-        <v>92293</v>
+        <v>57529</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,35 +1118,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1151,10 +1151,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465884</v>
+        <v>465919</v>
       </c>
       <c r="R6" t="n">
-        <v>6772194</v>
+        <v>6772218</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 14829-2025 artfynd.xlsx
+++ b/artfynd/A 14829-2025 artfynd.xlsx
@@ -893,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125017103</v>
+        <v>125017102</v>
       </c>
       <c r="B4" t="n">
-        <v>92293</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,47 +905,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kvarntjärn, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465884</v>
+        <v>465660</v>
       </c>
       <c r="R4" t="n">
-        <v>6772194</v>
+        <v>6771995</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1004,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125017102</v>
+        <v>125017103</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>92293</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1016,38 +1007,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kvarntjärn, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465660</v>
+        <v>465884</v>
       </c>
       <c r="R5" t="n">
-        <v>6771995</v>
+        <v>6772194</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 14829-2025 artfynd.xlsx
+++ b/artfynd/A 14829-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125017104</v>
+        <v>125017102</v>
       </c>
       <c r="B2" t="n">
-        <v>92293</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kvarntjärn, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465886</v>
+        <v>465660</v>
       </c>
       <c r="R2" t="n">
-        <v>6772198</v>
+        <v>6771995</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125017100</v>
+        <v>125017099</v>
       </c>
       <c r="B3" t="n">
-        <v>92328</v>
+        <v>57529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,34 +793,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kvarntjärn, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465685</v>
+        <v>465919</v>
       </c>
       <c r="R3" t="n">
-        <v>6771959</v>
+        <v>6772218</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-12</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125017102</v>
+        <v>125017103</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>92293</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,38 +896,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kvarntjärn, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465660</v>
+        <v>465884</v>
       </c>
       <c r="R4" t="n">
-        <v>6771995</v>
+        <v>6772194</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,7 +995,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125017103</v>
+        <v>125017104</v>
       </c>
       <c r="B5" t="n">
         <v>92293</v>
@@ -1044,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465884</v>
+        <v>465886</v>
       </c>
       <c r="R5" t="n">
-        <v>6772194</v>
+        <v>6772198</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,10 +1106,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125017099</v>
+        <v>125017100</v>
       </c>
       <c r="B6" t="n">
-        <v>57529</v>
+        <v>92328</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1122,39 +1122,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kvarntjärn, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465919</v>
+        <v>465685</v>
       </c>
       <c r="R6" t="n">
-        <v>6772218</v>
+        <v>6771959</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1187,6 +1182,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 14829-2025 artfynd.xlsx
+++ b/artfynd/A 14829-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125017102</v>
+        <v>125017103</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>92293</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kvarntjärn, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465660</v>
+        <v>465884</v>
       </c>
       <c r="R2" t="n">
-        <v>6771995</v>
+        <v>6772194</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125017099</v>
+        <v>125017104</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>92293</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,31 +798,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -822,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465919</v>
+        <v>465886</v>
       </c>
       <c r="R3" t="n">
-        <v>6772218</v>
+        <v>6772198</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125017103</v>
+        <v>125017099</v>
       </c>
       <c r="B4" t="n">
-        <v>92293</v>
+        <v>57529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,35 +909,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -933,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465884</v>
+        <v>465919</v>
       </c>
       <c r="R4" t="n">
-        <v>6772194</v>
+        <v>6772218</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125017104</v>
+        <v>125017100</v>
       </c>
       <c r="B5" t="n">
-        <v>92293</v>
+        <v>92328</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,47 +1016,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kvarntjärn, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465886</v>
+        <v>465685</v>
       </c>
       <c r="R5" t="n">
-        <v>6772198</v>
+        <v>6771959</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1080,6 +1080,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1106,10 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125017100</v>
+        <v>125017102</v>
       </c>
       <c r="B6" t="n">
-        <v>92328</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1122,21 +1127,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1146,10 +1151,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465685</v>
+        <v>465660</v>
       </c>
       <c r="R6" t="n">
-        <v>6771959</v>
+        <v>6771995</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1182,11 +1187,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-12</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 14829-2025 artfynd.xlsx
+++ b/artfynd/A 14829-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125017103</v>
+        <v>125017100</v>
       </c>
       <c r="B2" t="n">
-        <v>92293</v>
+        <v>92328</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kvarntjärn, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465884</v>
+        <v>465685</v>
       </c>
       <c r="R2" t="n">
-        <v>6772194</v>
+        <v>6771959</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125017104</v>
+        <v>125017099</v>
       </c>
       <c r="B3" t="n">
-        <v>92293</v>
+        <v>57529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,35 +794,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -835,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465886</v>
+        <v>465919</v>
       </c>
       <c r="R3" t="n">
-        <v>6772198</v>
+        <v>6772218</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125017099</v>
+        <v>125017103</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>92293</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,31 +901,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -942,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465919</v>
+        <v>465884</v>
       </c>
       <c r="R4" t="n">
-        <v>6772218</v>
+        <v>6772194</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1004,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125017100</v>
+        <v>125017104</v>
       </c>
       <c r="B5" t="n">
-        <v>92328</v>
+        <v>92293</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1016,38 +1012,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kvarntjärn, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465685</v>
+        <v>465886</v>
       </c>
       <c r="R5" t="n">
-        <v>6771959</v>
+        <v>6772198</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1080,11 +1085,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-12</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 14829-2025 artfynd.xlsx
+++ b/artfynd/A 14829-2025 artfynd.xlsx
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125017103</v>
+        <v>125017104</v>
       </c>
       <c r="B4" t="n">
         <v>92293</v>
@@ -938,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465884</v>
+        <v>465886</v>
       </c>
       <c r="R4" t="n">
-        <v>6772194</v>
+        <v>6772198</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,7 +1000,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125017104</v>
+        <v>125017103</v>
       </c>
       <c r="B5" t="n">
         <v>92293</v>
@@ -1049,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465886</v>
+        <v>465884</v>
       </c>
       <c r="R5" t="n">
-        <v>6772198</v>
+        <v>6772194</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 14829-2025 artfynd.xlsx
+++ b/artfynd/A 14829-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125017100</v>
+        <v>125017102</v>
       </c>
       <c r="B2" t="n">
-        <v>92328</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465685</v>
+        <v>465660</v>
       </c>
       <c r="R2" t="n">
-        <v>6771959</v>
+        <v>6771995</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-12</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125017099</v>
+        <v>125017103</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>92293</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,31 +789,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -827,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465919</v>
+        <v>465884</v>
       </c>
       <c r="R3" t="n">
-        <v>6772218</v>
+        <v>6772194</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125017104</v>
+        <v>125017100</v>
       </c>
       <c r="B4" t="n">
-        <v>92293</v>
+        <v>92328</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,47 +900,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kvarntjärn, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465886</v>
+        <v>465685</v>
       </c>
       <c r="R4" t="n">
-        <v>6772198</v>
+        <v>6771959</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,6 +964,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1000,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125017103</v>
+        <v>125017099</v>
       </c>
       <c r="B5" t="n">
-        <v>92293</v>
+        <v>57529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,35 +1007,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1049,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465884</v>
+        <v>465919</v>
       </c>
       <c r="R5" t="n">
-        <v>6772194</v>
+        <v>6772218</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,10 +1102,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125017102</v>
+        <v>125017104</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>92293</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,38 +1114,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kvarntjärn, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465660</v>
+        <v>465886</v>
       </c>
       <c r="R6" t="n">
-        <v>6771995</v>
+        <v>6772198</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 14829-2025 artfynd.xlsx
+++ b/artfynd/A 14829-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125017102</v>
+        <v>125017099</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>57632</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kvarntjärn, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465660</v>
+        <v>465919</v>
       </c>
       <c r="R2" t="n">
-        <v>6771995</v>
+        <v>6772218</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125017103</v>
+        <v>125017104</v>
       </c>
       <c r="B3" t="n">
-        <v>92293</v>
+        <v>92448</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -826,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465884</v>
+        <v>465886</v>
       </c>
       <c r="R3" t="n">
-        <v>6772194</v>
+        <v>6772198</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125017100</v>
+        <v>125017102</v>
       </c>
       <c r="B4" t="n">
-        <v>92328</v>
+        <v>78947</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,21 +909,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465685</v>
+        <v>465660</v>
       </c>
       <c r="R4" t="n">
-        <v>6771959</v>
+        <v>6771995</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,11 +969,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-12</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -995,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125017099</v>
+        <v>125017100</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
+        <v>92484</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,39 +1011,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kvarntjärn, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465919</v>
+        <v>465685</v>
       </c>
       <c r="R5" t="n">
-        <v>6772218</v>
+        <v>6771959</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,6 +1071,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1102,10 +1102,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125017104</v>
+        <v>125017103</v>
       </c>
       <c r="B6" t="n">
-        <v>92293</v>
+        <v>92448</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,10 +1151,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465886</v>
+        <v>465884</v>
       </c>
       <c r="R6" t="n">
-        <v>6772198</v>
+        <v>6772194</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 14829-2025 artfynd.xlsx
+++ b/artfynd/A 14829-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125017099</v>
+        <v>125017100</v>
       </c>
       <c r="B2" t="n">
-        <v>57632</v>
+        <v>92484</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kvarntjärn, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465919</v>
+        <v>465685</v>
       </c>
       <c r="R2" t="n">
-        <v>6772218</v>
+        <v>6771959</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -995,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125017100</v>
+        <v>125017099</v>
       </c>
       <c r="B5" t="n">
-        <v>92484</v>
+        <v>57632</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,34 +1011,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kvarntjärn, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465685</v>
+        <v>465919</v>
       </c>
       <c r="R5" t="n">
-        <v>6771959</v>
+        <v>6772218</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,11 +1076,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-12</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 14829-2025 artfynd.xlsx
+++ b/artfynd/A 14829-2025 artfynd.xlsx
@@ -675,50 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125017100</v>
+        <v>125017104</v>
       </c>
       <c r="B2" t="n">
-        <v>92484</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92448</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kvarntjärn, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465685</v>
+        <v>465886</v>
       </c>
       <c r="R2" t="n">
-        <v>6771959</v>
+        <v>6772198</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +755,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-12</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,16 +781,11 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125017104</v>
+        <v>125017103</v>
       </c>
       <c r="B3" t="n">
         <v>92448</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>LC</t>
@@ -831,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465886</v>
+        <v>465884</v>
       </c>
       <c r="R3" t="n">
-        <v>6772198</v>
+        <v>6772194</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,15 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125017102</v>
+        <v>125017099</v>
       </c>
       <c r="B4" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57632</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -909,34 +898,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kvarntjärn, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465660</v>
+        <v>465919</v>
       </c>
       <c r="R4" t="n">
-        <v>6771995</v>
+        <v>6772218</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,15 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125017099</v>
+        <v>125017100</v>
       </c>
       <c r="B5" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92484</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1011,39 +1000,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kvarntjärn, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465919</v>
+        <v>465685</v>
       </c>
       <c r="R5" t="n">
-        <v>6772218</v>
+        <v>6771959</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,6 +1060,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1102,59 +1091,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125017103</v>
+        <v>125017102</v>
       </c>
       <c r="B6" t="n">
-        <v>92448</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kvarntjärn, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465884</v>
+        <v>465660</v>
       </c>
       <c r="R6" t="n">
-        <v>6772194</v>
+        <v>6771995</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
